--- a/docs/security-audit-vulnerabilities-2026-08-14.xlsx
+++ b/docs/security-audit-vulnerabilities-2026-08-14.xlsx
@@ -7,12 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="漏洞清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="后端接口修复对照" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="漏洞修复对照表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'漏洞清单'!$A$3:$J$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'后端接口修复对照'!$A$2:$D$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'漏洞修复对照表'!$A$3:$J$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="7">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -62,8 +62,23 @@
       <b val="1"/>
       <color rgb="007F6000"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -90,6 +105,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -101,43 +121,59 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00C9C9C9"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00C9C9C9"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00C9C9C9"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D0D0"/>
+        <color rgb="00C9C9C9"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -213,6 +249,143 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>漏洞风险等级分布</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'漏洞修复对照表'!B20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'漏洞修复对照表'!$A$21:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'漏洞修复对照表'!$B$21:$B$24</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>风险等级</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>数量</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -504,14 +677,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="46" customWidth="1" min="7" max="7"/>
     <col width="40" customWidth="1" min="8" max="8"/>
@@ -529,7 +702,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>审计日期：2026-08-14  |  范围：访问控制 / RBAC 权限审计  |  共 13 项（高危 2 / 中危 5 / 低 6）</t>
+          <t>审计日期：2026-08-14  |  范围：访问控制 / RBAC 权限审计  |  共 13 项（高危 2 / 中危 5 / 低 6）  |  全部已修复</t>
         </is>
       </c>
     </row>
@@ -591,47 +764,47 @@
           <t>SEC-01</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>高危</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>数据库备份接口未授权，可下载含密码哈希的数据库</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>GET /api/system/backup</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>server/src/routes/system.ts</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>未授权敏感数据下载（Broken Access Control）</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>导出整个面板 SQLite 数据库（含用户口令哈希、镜像源配置、操作日志等），审计前未加 requireAdmin，普通用户可下载。</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>口令哈希可被离线破解；镜像源配置（可能含私有仓库凭据）泄露；拖库。</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>补 requireAdmin；前端设置页「导出备份」按钮及 handleBackup 函数同步加管理员守卫。</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
@@ -643,947 +816,716 @@
           <t>SEC-02</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>高危</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>网络清理接口未授权，可一键破坏网络配置</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>POST /api/networks/prune</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>server/src/routes/networks.ts</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>不可逆的未授权破坏性操作</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>批量断开并删除所有未被容器连接的自定义网络，审计前未加 requireAdmin。</t>
         </is>
       </c>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>清除全部未使用网络，影响依赖自定义网络的应用编排。</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>补 requireAdmin。</t>
         </is>
       </c>
-      <c r="J5" s="4" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>SEC-03</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>用户枚举：GET /api/system/users 未授权</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>GET /api/system/users</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>server/src/routes/system.ts</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>信息泄露 / 用户枚举</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>返回全部用户名与角色，审计前未受保护。</t>
         </is>
       </c>
-      <c r="H6" s="5" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>普通用户可枚举账户，为口令爆破或社工提供信息基础。</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>补 requireAdmin。</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>SEC-04</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>操作日志查询与导出未授权</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>GET /api/operation-logs、GET /api/operation-logs/export</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>server/src/routes/operationLogs.ts</t>
         </is>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>信息泄露</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="inlineStr">
         <is>
           <t>含用户名、操作记录、目标资源等审计数据，审计前两者均未受保护（仅 DELETE 清空受限）。</t>
         </is>
       </c>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>普通用户可查看/导出全部操作审计日志，了解他人操作与系统拓扑。</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>两个 GET 均补 requireAdmin。</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>SEC-05</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>宿主机文件系统遍历未授权</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>GET /api/hostfiles/list</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>server/src/routes/hostFiles.ts</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>信息泄露 / 路径遍历</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="inlineStr">
         <is>
           <t>返回指定路径的目录/文件名、类型、大小、修改时间，审计前未受保护。</t>
         </is>
       </c>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>普通用户可遍历宿主文件系统结构，为后续攻击提供侦察。</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>补 requireAdmin。</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>SEC-06</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>数据库实例更新接口未授权（可改凭据/连接配置）</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>PUT /api/databases/:id</t>
         </is>
       </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>server/src/routes/databases.ts</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>越权配置修改</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="inlineStr">
         <is>
           <t>更新数据库实例的宿主/端口/用户/口令/连接信息，审计前未加 requireAdmin。</t>
         </is>
       </c>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>普通用户可篡改数据库连接凭据导向恶意地址，或破坏其可连接性。</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>补 requireAdmin；前端「编辑实例」入口同步限管理员。</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>SEC-07</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>终端会话信息未授权</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>GET /api/hostterminal/info</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>server/src/routes/hostTerminal.ts</t>
         </is>
       </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>信息泄露（保持一致收口）</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>返回宿主机会话工作目录与可用 shell，审计前未受保护。</t>
         </is>
       </c>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>轻度信息泄露；终端系高危面，应收口一致。</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>补 requireAdmin。</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>SEC-08</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>容器生命周期操作权限边界曾被错误收紧</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t>CONTAINERS start/stop/restart/pause/unpause</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>server/src/routes/containers.ts</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>权限模型 / 一致性</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>审计过程中曾一度将生命周期操作全部设为 requireAdmin，与竞品共识不符、过度限制普通用户。</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>普通用户无法启停/重启/暂停容器，与主流面板（Portainer/K8s）体验不一致。</t>
         </is>
       </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>依据竞品调研恢复开放给普通用户；仅保留重命名、克隆为仅管理员，并补齐 /:id/clone 的 requireAdmin。</t>
         </is>
       </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>SEC-09</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>容器「清理未使用」入口前端未联动</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t>confirmPrune / /api/system/prune</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>web/src/pages/containers.tsx</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr">
         <is>
           <t>前端未联动</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>调系统级清理接口（本就 admin），但前端清理按钮/函数未做管理员禁用与守卫。</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>普通用户可看到入口，点击后由后端拦截（403）。</t>
         </is>
       </c>
-      <c r="I12" s="6" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>前端补 disabled 与函数守卫。</t>
         </is>
       </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>SEC-10</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>容器重命名按钮前端未联动</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>openRename / confirmRename</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>web/src/pages/containers.tsx</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t>前端未联动</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="9" t="inlineStr">
         <is>
           <t>后端 rename 需 admin，但前端按钮未禁用、函数未守卫。</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>普通用户可看到入口，操作被后端拦截。</t>
         </is>
       </c>
-      <c r="I13" s="6" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>前端补 disabled 与函数守卫。</t>
         </is>
       </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>SEC-11</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>容器克隆按钮前端未联动</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>openClone / confirmClone</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>web/src/pages/containers.tsx</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>前端未联动</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>后端 clone 需 admin，前端入口未禁用、函数未守卫。</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>普通用户可看到入口，操作被后端拦截。</t>
         </is>
       </c>
-      <c r="I14" s="6" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>前端补 disabled 与函数守卫。</t>
         </is>
       </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="8" t="inlineStr">
         <is>
           <t>SEC-12</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>数据库实例「登记/编辑」前端需限管理员</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t>POST /（登记）、PUT /:id（更新）</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>web/src/pages/databases.tsx</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t>前端未联动</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="9" t="inlineStr">
         <is>
           <t>后端登记与更新均需 admin，前端编辑入口与提交未对普通用户禁用。</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>普通用户可看到编辑入口，提交被后端拦截。</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>前端补管理员禁用/守卫，并同步 useCallback 依赖。</t>
         </is>
       </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>SEC-13</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>低</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
         <is>
           <t>应用商店、镜像中心、构建、宿主机文件等页面写入口未联动</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t>appstore/hub/build/hostFiles/sites/compose/backups/cloudBackup/images/tasks 各写操作按钮</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="9" t="inlineStr">
         <is>
           <t>web/src/pages/{appstore,hub,build,hostFiles,sites,compose,backups,cloudBackup,images,tasks}.tsx</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t>前端未联动</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="9" t="inlineStr">
         <is>
           <t>这些页面对应后端写操作均为 requireAdmin，但前端各安装/拉取/构建/写文件/站点/备份/镜像/任务按钮初始未做管理员禁用。</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>普通用户可看到入口，写操作被后端拦截。</t>
         </is>
       </c>
-      <c r="I16" s="6" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>统一补 canManage 禁用态与函数级守卫；并为 sites /reload、build /image、images 系列补齐后端 requireAdmin 或前端联动。</t>
         </is>
       </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>✅ 已修复</t>
         </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>统计汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>风险等级</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>数量</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="B21" s="13">
+        <f>COUNTIF($B$4:$B$16,A21)</f>
+        <v/>
+      </c>
+      <c r="C21" s="14">
+        <f>IF(COUNTA($A$4:$A$16)=0,"",B21/COUNTA($A$4:$A$16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="B22" s="13">
+        <f>COUNTIF($B$4:$B$16,A22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="14">
+        <f>IF(COUNTA($A$4:$A$16)=0,"",B22/COUNTA($A$4:$A$16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="B23" s="13">
+        <f>COUNTIF($B$4:$B$16,A23)</f>
+        <v/>
+      </c>
+      <c r="C23" s="14">
+        <f>IF(COUNTA($A$4:$A$16)=0,"",B23/COUNTA($A$4:$A$16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B24" s="13">
+        <f>SUBTOTAL(3,$B$4:$B$16)</f>
+        <v/>
+      </c>
+      <c r="C24" s="14">
+        <f>IF(COUNTA($A$4:$A$16)=0,"",COUNTA($A$4:$A$16)/COUNTA($A$4:$A$16))</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A3:J16"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>后端接口 requireAdmin 修复对照</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>接口</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>文件</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>关联漏洞</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>GET /api/system/backup</t>
-        </is>
-      </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/system.ts</t>
-        </is>
-      </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>✅ 已修复</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>SEC-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>GET /api/system/users</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/system.ts</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>✅ 已修复</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>SEC-03</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>GET /api/operation-logs、/export</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/operationLogs.ts</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>✅ 已修复</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>SEC-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>GET /api/hostfiles/list</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/hostFiles.ts</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>✅ 已修复</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>SEC-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>GET /api/hostterminal/info</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/hostTerminal.ts</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>✅ 已修复</t>
-        </is>
-      </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t>SEC-07</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>DELETE /api/operation-logs</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/operationLogs.ts</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>✅（审计前已正确）</t>
-        </is>
-      </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>POST /api/networks/prune</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/networks.ts</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>✅ 已修复</t>
-        </is>
-      </c>
-      <c r="D9" s="8" t="inlineStr">
-        <is>
-          <t>SEC-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>PUT /api/databases/:id</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/databases.ts</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>✅ 已修复</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>SEC-06</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>POST /api/containers/:id/clone</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/containers.ts</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>✅ 已修复</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>SEC-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>CONTAINERS start/stop/restart/pause/unpause</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/containers.ts</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>✅ 恢复为普通用户可用（按竞品共识）</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>SEC-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>POST /api/containers/:id/rename</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="inlineStr">
-        <is>
-          <t>server/src/routes/containers.ts</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>✅ 设为仅管理员</t>
-        </is>
-      </c>
-      <c r="D13" s="8" t="inlineStr">
-        <is>
-          <t>SEC-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>其余写路由（镜像/卷/引擎/任务/备份/站点/云端/应用商店/镜像中心/构建/宿主文件/终端）</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>各 routes</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>✅ 审计前已 / 本次已补齐</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>SEC-13</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:D14"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>